--- a/agriculture 5.xlsx
+++ b/agriculture 5.xlsx
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
-  <si>
-    <t xml:space="preserve">ANNUAL GROWTH RATE OF AREA, PRODUCTION, YIELD OF WHEAT IN INDIA(1950-2022)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
   <si>
     <t xml:space="preserve">YEAR</t>
   </si>
@@ -299,11 +296,12 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -319,14 +317,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -407,16 +397,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -432,7 +418,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -444,7 +430,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -465,1103 +451,1093 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
-  <sheetFormatPr defaultColWidth="10.76953125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E1048576"/>
+  <sheetFormatPr defaultColWidth="10.78515625" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24.8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20.03"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="A3" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
         <v>6</v>
       </c>
+      <c r="B4" s="2" t="n">
+        <v>-2.87179487179486</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>-4.33436532507741</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>-1.50476937937695</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>-2.87179487179486</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>-4.33436532507741</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>-1.50476937937695</v>
+      <c r="B5" s="2" t="n">
+        <v>3.80147835269271</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>21.3592233009709</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>16.9141421106667</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>3.80147835269271</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>21.3592233009709</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>16.9141421106667</v>
+      <c r="B6" s="2" t="n">
+        <v>8.646998982706</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>6.93333333333333</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>-1.69993577729137</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="3" t="n">
-        <v>8.646998982706</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>6.93333333333333</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>-1.69993577729137</v>
+      <c r="B7" s="2" t="n">
+        <v>5.43071161048689</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>12.7182044887781</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>7.04533333333335</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>5.43071161048689</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>12.7182044887781</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>7.04533333333335</v>
+      <c r="B8" s="2" t="n">
+        <v>9.85790408525755</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>-3.09734513274336</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>-11.7931343729759</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="3" t="n">
-        <v>9.85790408525755</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>-3.09734513274336</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>-11.7931343729759</v>
+      <c r="B9" s="2" t="n">
+        <v>9.29668552950687</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>7.30593607305936</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>-1.82021012200633</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="3" t="n">
-        <v>9.29668552950687</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>7.30593607305936</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>-1.82021012200633</v>
+      <c r="B10" s="2" t="n">
+        <v>-13.2396449704142</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>-15</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>-1.90861104319185</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="3" t="n">
-        <v>-13.2396449704142</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>-15</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>-1.90861104319185</v>
+      <c r="B11" s="2" t="n">
+        <v>7.58738277919862</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>24.6558197747184</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>15.7214076246334</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="3" t="n">
-        <v>7.58738277919862</v>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>24.6558197747184</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>15.7214076246334</v>
+      <c r="B12" s="2" t="n">
+        <v>6.02218700475436</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>3.6144578313253</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>-2.18190111755912</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="3" t="n">
-        <v>6.02218700475436</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>3.6144578313253</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>-2.18190111755912</v>
+      <c r="B13" s="2" t="n">
+        <v>-3.36322869955158</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>6.5891472868217</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>10.1981865284974</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="3" t="n">
-        <v>-3.36322869955158</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>6.5891472868217</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>10.1981865284974</v>
+      <c r="B14" s="2" t="n">
+        <v>4.94972931167828</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>9.72727272727274</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>4.61603563997979</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="3" t="n">
-        <v>4.94972931167828</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>9.72727272727274</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>4.61603563997979</v>
+      <c r="B15" s="2" t="n">
+        <v>0.147383935151058</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>-10.6876553438277</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>-10.8730337078652</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="3" t="n">
-        <v>0.147383935151058</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>-10.6876553438277</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>-10.8730337078652</v>
+      <c r="B16" s="2" t="n">
+        <v>-0.662251655629143</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>-8.62708719851577</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>-8.01785106463447</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="3" t="n">
-        <v>-0.662251655629143</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>-8.62708719851577</v>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>-8.01785106463447</v>
+      <c r="B17" s="2" t="n">
+        <v>-0.592592592592589</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>24.4670050761421</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>25.1319161766923</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="3" t="n">
-        <v>-0.592592592592589</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>24.4670050761421</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>25.1319161766923</v>
+      <c r="B18" s="2" t="n">
+        <v>-6.3338301043219</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>-15.1712887438825</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>-9.3789704271632</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="3" t="n">
-        <v>-6.3338301043219</v>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>-15.1712887438825</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>-9.3789704271632</v>
+      <c r="B19" s="2" t="n">
+        <v>2.14797136038185</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>9.51923076923078</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>7.21563508466587</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="3" t="n">
-        <v>2.14797136038185</v>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>9.51923076923078</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>7.21563508466587</v>
+      <c r="B20" s="2" t="n">
+        <v>16.7445482866044</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>45.2151009657594</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>24.3870269539044</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="3" t="n">
-        <v>16.7445482866044</v>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>45.2151009657594</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>24.3870269539044</v>
+      <c r="B21" s="2" t="n">
+        <v>6.47098065376919</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>12.7569528415961</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>5.90447707087183</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="3" t="n">
-        <v>6.47098065376919</v>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>12.7569528415961</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>5.90447707087183</v>
+      <c r="B22" s="2" t="n">
+        <v>4.19799498746867</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>7.7211796246649</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>3.37597877711695</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="3" t="n">
-        <v>4.19799498746867</v>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>7.7211796246649</v>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>3.37597877711695</v>
+      <c r="B23" s="2" t="n">
+        <v>9.68129885748648</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>18.6162269785963</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>8.19536423841059</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="3" t="n">
-        <v>9.68129885748648</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>18.6162269785963</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>8.19536423841059</v>
+      <c r="B24" s="2" t="n">
+        <v>4.9342105263158</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>10.8266890474192</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>5.57230298393268</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="3" t="n">
-        <v>4.9342105263158</v>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>10.8266890474192</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>5.57230298393268</v>
+      <c r="B25" s="2" t="n">
+        <v>1.67189132706373</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>-6.32336236274139</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>-7.86328750643195</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="3" t="n">
-        <v>1.67189132706373</v>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>-6.32336236274139</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>-7.86328750643195</v>
+      <c r="B26" s="2" t="n">
+        <v>-4.52209660842756</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>-11.9644300727567</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>-7.79498635287454</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="3" t="n">
-        <v>-4.52209660842756</v>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>-11.9644300727567</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>-7.79498635287454</v>
+      <c r="B27" s="2" t="n">
+        <v>-3.06781485468244</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>10.6519742883379</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>14.15421888196</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="3" t="n">
-        <v>-3.06781485468244</v>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>10.6519742883379</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>14.15421888196</v>
+      <c r="B28" s="2" t="n">
+        <v>13.5480288728484</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>19.6680497925311</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>5.38953032171281</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="3" t="n">
-        <v>13.5480288728484</v>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>19.6680497925311</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>5.38953032171281</v>
+      <c r="B29" s="2" t="n">
+        <v>2.29828850855747</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>0.589459084604727</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>-1.67060208328901</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="3" t="n">
-        <v>2.29828850855747</v>
-      </c>
-      <c r="C30" s="3" t="n">
-        <v>0.589459084604727</v>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>-1.67060208328901</v>
+      <c r="B30" s="2" t="n">
+        <v>2.58126195028681</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>9.44501895897967</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>6.72743399845677</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="3" t="n">
-        <v>2.58126195028681</v>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>9.44501895897967</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>6.72743399845677</v>
+      <c r="B31" s="2" t="n">
+        <v>5.4986020503262</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>11.8425196850394</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>5.97702702702703</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="3" t="n">
-        <v>5.4986020503262</v>
-      </c>
-      <c r="C32" s="3" t="n">
-        <v>11.8425196850394</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>5.97702702702703</v>
+      <c r="B32" s="2" t="n">
+        <v>-2.07597173144876</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>-10.3632779498733</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>-8.46307843362279</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="3" t="n">
-        <v>-2.07597173144876</v>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>-10.3632779498733</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>-8.46307843362279</v>
+      <c r="B33" s="2" t="n">
+        <v>0.496165990076669</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>14.0747722274584</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>13.5116875156716</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="3" t="n">
-        <v>0.496165990076669</v>
-      </c>
-      <c r="C34" s="3" t="n">
-        <v>14.0747722274584</v>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>13.5116875156716</v>
+      <c r="B34" s="2" t="n">
+        <v>-0.628366247755841</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>3.13963095565959</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>3.76079179731363</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="3" t="n">
-        <v>-0.628366247755841</v>
-      </c>
-      <c r="C35" s="3" t="n">
-        <v>3.13963095565959</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>3.76079179731363</v>
+      <c r="B35" s="2" t="n">
+        <v>6.45889792231256</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>14.2590120160214</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>7.39207569485512</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="3" t="n">
-        <v>6.45889792231256</v>
-      </c>
-      <c r="C36" s="3" t="n">
-        <v>14.2590120160214</v>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>7.39207569485512</v>
+      <c r="B36" s="2" t="n">
+        <v>4.66694951209166</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>6.28651554101425</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>1.48678414096917</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="3" t="n">
-        <v>4.66694951209166</v>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>6.28651554101425</v>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>1.48678414096917</v>
+      <c r="B37" s="2" t="n">
+        <v>-4.49939197405758</v>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>-3.10026385224273</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>1.46500271296799</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="3" t="n">
-        <v>-4.49939197405758</v>
-      </c>
-      <c r="C38" s="3" t="n">
-        <v>-3.10026385224273</v>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>1.46500271296799</v>
+      <c r="B38" s="2" t="n">
+        <v>-2.37691001697793</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>6.761969593828</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>9.39304812834225</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="3" t="n">
-        <v>-2.37691001697793</v>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>6.761969593828</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>9.39304812834225</v>
+      <c r="B39" s="2" t="n">
+        <v>0.565217391304351</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>-5.80233793836343</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>-6.3314838804292</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="3" t="n">
-        <v>0.565217391304351</v>
-      </c>
-      <c r="C40" s="3" t="n">
-        <v>-5.80233793836343</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>-6.3314838804292</v>
+      <c r="B40" s="2" t="n">
+        <v>-0.302637267617811</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>4.17418772563176</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>4.49030076247436</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="3" t="n">
-        <v>-0.302637267617811</v>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>4.17418772563176</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>4.49030076247436</v>
+      <c r="B41" s="2" t="n">
+        <v>4.55333911535125</v>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>17.1973142733377</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>12.0933786841277</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="3" t="n">
-        <v>4.55333911535125</v>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>17.1973142733377</v>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>12.0933786841277</v>
+      <c r="B42" s="2" t="n">
+        <v>-2.53007051016175</v>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>-7.87285159859545</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>-5.48144187497215</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="3" t="n">
-        <v>-2.53007051016175</v>
-      </c>
-      <c r="C43" s="3" t="n">
-        <v>-7.87285159859545</v>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>-5.48144187497215</v>
+      <c r="B43" s="2" t="n">
+        <v>2.85106382978724</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>10.6118355065196</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>7.54544426006938</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="B44" s="3" t="n">
-        <v>2.85106382978724</v>
-      </c>
-      <c r="C44" s="3" t="n">
-        <v>10.6118355065196</v>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>7.54544426006938</v>
+      <c r="B44" s="2" t="n">
+        <v>-3.76499793131981</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>0.997461008342393</v>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>4.94884585375259</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="3" t="n">
-        <v>-3.76499793131981</v>
-      </c>
-      <c r="C45" s="3" t="n">
-        <v>0.997461008342393</v>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v>4.94884585375259</v>
+      <c r="B45" s="2" t="n">
+        <v>5.71797076526224</v>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>2.72939486442809</v>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>-2.82678428227746</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
         <v>48</v>
       </c>
-      <c r="B46" s="3" t="n">
-        <v>5.71797076526224</v>
-      </c>
-      <c r="C46" s="3" t="n">
-        <v>2.72939486442809</v>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v>-2.82678428227746</v>
+      <c r="B46" s="2" t="n">
+        <v>2.27734851565677</v>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>4.59709840936899</v>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>2.29695344199161</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
         <v>49</v>
       </c>
-      <c r="B47" s="3" t="n">
-        <v>2.27734851565677</v>
-      </c>
-      <c r="C47" s="3" t="n">
-        <v>4.59709840936899</v>
-      </c>
-      <c r="D47" s="3" t="n">
-        <v>2.29695344199161</v>
+      <c r="B47" s="2" t="n">
+        <v>2.18687872763419</v>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>9.90975935828875</v>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>7.52689075630251</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="3" t="n">
-        <v>2.18687872763419</v>
-      </c>
-      <c r="C48" s="3" t="n">
-        <v>9.90975935828875</v>
-      </c>
-      <c r="D48" s="3" t="n">
-        <v>7.52689075630251</v>
+      <c r="B48" s="2" t="n">
+        <v>-2.68482490272373</v>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>-5.5800516953018</v>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>-2.97482748110692</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="3" t="n">
-        <v>-2.68482490272373</v>
-      </c>
-      <c r="C49" s="3" t="n">
-        <v>-5.5800516953018</v>
-      </c>
-      <c r="D49" s="3" t="n">
-        <v>-2.97482748110692</v>
+      <c r="B49" s="2" t="n">
+        <v>3.5185925629748</v>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>11.6747181964573</v>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>7.87874394384234</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="B50" s="3" t="n">
-        <v>3.5185925629748</v>
-      </c>
-      <c r="C50" s="3" t="n">
-        <v>11.6747181964573</v>
-      </c>
-      <c r="D50" s="3" t="n">
-        <v>7.87874394384234</v>
+      <c r="B50" s="2" t="n">
+        <v>3.12862108922363</v>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>-4.32588320115357</v>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>-7.22829495564913</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="3" t="n">
-        <v>3.12862108922363</v>
-      </c>
-      <c r="C51" s="3" t="n">
-        <v>-4.32588320115357</v>
-      </c>
-      <c r="D51" s="3" t="n">
-        <v>-7.22829495564913</v>
+      <c r="B51" s="2" t="n">
+        <v>3.07116104868914</v>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>7.44536548605881</v>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>4.24382902350886</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="3" t="n">
-        <v>3.07116104868914</v>
-      </c>
-      <c r="C52" s="3" t="n">
-        <v>7.44536548605881</v>
-      </c>
-      <c r="D52" s="3" t="n">
-        <v>4.24382902350886</v>
+      <c r="B52" s="2" t="n">
+        <v>-0.109011627906985</v>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>7.12582409875158</v>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>7.23881288409869</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
         <v>55</v>
       </c>
-      <c r="B53" s="3" t="n">
-        <v>-0.109011627906985</v>
-      </c>
-      <c r="C53" s="3" t="n">
-        <v>7.12582409875158</v>
-      </c>
-      <c r="D53" s="3" t="n">
-        <v>7.23881288409869</v>
+      <c r="B53" s="2" t="n">
+        <v>-6.4023281193161</v>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>-8.75998428702369</v>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>-2.51979841612671</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="3" t="n">
-        <v>-6.4023281193161</v>
-      </c>
-      <c r="C54" s="3" t="n">
-        <v>-8.75998428702369</v>
-      </c>
-      <c r="D54" s="3" t="n">
-        <v>-2.51979841612671</v>
+      <c r="B54" s="2" t="n">
+        <v>2.37077341624563</v>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>4.43455797933408</v>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>1.99409158050221</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
         <v>57</v>
       </c>
-      <c r="B55" s="3" t="n">
-        <v>2.37077341624563</v>
-      </c>
-      <c r="C55" s="3" t="n">
-        <v>4.43455797933408</v>
-      </c>
-      <c r="D55" s="3" t="n">
-        <v>1.99409158050221</v>
+      <c r="B55" s="2" t="n">
+        <v>-4.32801822323463</v>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>-9.6330905592964</v>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>-5.52063721940623</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
         <v>58</v>
       </c>
-      <c r="B56" s="3" t="n">
-        <v>-4.32801822323463</v>
-      </c>
-      <c r="C56" s="3" t="n">
-        <v>-9.6330905592964</v>
-      </c>
-      <c r="D56" s="3" t="n">
-        <v>-5.52063721940623</v>
+      <c r="B56" s="2" t="n">
+        <v>5.51587301587302</v>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>9.73236009732359</v>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>3.96548024157699</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
         <v>59</v>
       </c>
-      <c r="B57" s="3" t="n">
-        <v>5.51587301587302</v>
-      </c>
-      <c r="C57" s="3" t="n">
-        <v>9.73236009732359</v>
-      </c>
-      <c r="D57" s="3" t="n">
-        <v>3.96548024157699</v>
+      <c r="B57" s="2" t="n">
+        <v>-0.789770590447536</v>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>-4.8780487804878</v>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>-4.09141172134169</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
         <v>60</v>
       </c>
-      <c r="B58" s="3" t="n">
-        <v>-0.789770590447536</v>
-      </c>
-      <c r="C58" s="3" t="n">
-        <v>-4.8780487804878</v>
-      </c>
-      <c r="D58" s="3" t="n">
-        <v>-4.09141172134169</v>
+      <c r="B58" s="2" t="n">
+        <v>0.379075056861256</v>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>1.03438228438228</v>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>0.653343581860111</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="B59" s="3" t="n">
-        <v>0.379075056861256</v>
-      </c>
-      <c r="C59" s="3" t="n">
-        <v>1.03438228438228</v>
-      </c>
-      <c r="D59" s="3" t="n">
-        <v>0.653343581860111</v>
+      <c r="B59" s="2" t="n">
+        <v>5.70241691842899</v>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>9.31506849315069</v>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>3.39480717831233</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
         <v>62</v>
       </c>
-      <c r="B60" s="3" t="n">
-        <v>5.70241691842899</v>
-      </c>
-      <c r="C60" s="3" t="n">
-        <v>9.31506849315069</v>
-      </c>
-      <c r="D60" s="3" t="n">
-        <v>3.39480717831233</v>
+      <c r="B60" s="2" t="n">
+        <v>0.178635226866741</v>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>3.64068064899088</v>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>3.47722043937946</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="3" t="n">
-        <v>0.178635226866741</v>
-      </c>
-      <c r="C61" s="3" t="n">
-        <v>3.64068064899088</v>
-      </c>
-      <c r="D61" s="3" t="n">
-        <v>3.47722043937946</v>
+      <c r="B61" s="2" t="n">
+        <v>-1.0342368045649</v>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>2.68550337278861</v>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>3.7486572426813</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="B62" s="3" t="n">
-        <v>-1.0342368045649</v>
-      </c>
-      <c r="C62" s="3" t="n">
-        <v>2.68550337278861</v>
-      </c>
-      <c r="D62" s="3" t="n">
-        <v>3.7486572426813</v>
+      <c r="B62" s="2" t="n">
+        <v>2.55855855855855</v>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>0.148735746157658</v>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>-2.33152512288838</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="B63" s="3" t="n">
-        <v>2.55855855855855</v>
-      </c>
-      <c r="C63" s="3" t="n">
-        <v>0.148735746157658</v>
-      </c>
-      <c r="D63" s="3" t="n">
-        <v>-2.33152512288838</v>
+      <c r="B63" s="2" t="n">
+        <v>2.14335910049193</v>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>7.51237623762377</v>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>5.25194324013059</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
         <v>66</v>
       </c>
-      <c r="B64" s="3" t="n">
-        <v>2.14335910049193</v>
-      </c>
-      <c r="C64" s="3" t="n">
-        <v>7.51237623762377</v>
-      </c>
-      <c r="D64" s="3" t="n">
-        <v>5.25194324013059</v>
+      <c r="B64" s="2" t="n">
+        <v>2.71757825937393</v>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>9.22067457119833</v>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>6.30895614783584</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="B65" s="3" t="n">
-        <v>2.71757825937393</v>
-      </c>
-      <c r="C65" s="3" t="n">
-        <v>9.22067457119833</v>
-      </c>
-      <c r="D65" s="3" t="n">
-        <v>6.30895614783584</v>
+      <c r="B65" s="2" t="n">
+        <v>0.468854655056927</v>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>-1.44392917369307</v>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>-1.90274442160661</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="B66" s="3" t="n">
-        <v>0.468854655056927</v>
-      </c>
-      <c r="C66" s="3" t="n">
-        <v>-1.44392917369307</v>
-      </c>
-      <c r="D66" s="3" t="n">
-        <v>-1.90274442160661</v>
+      <c r="B66" s="2" t="n">
+        <v>1.56666666666667</v>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>2.502406159769</v>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>0.925385202821083</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
         <v>69</v>
       </c>
-      <c r="B67" s="3" t="n">
-        <v>1.56666666666667</v>
-      </c>
-      <c r="C67" s="3" t="n">
-        <v>2.502406159769</v>
-      </c>
-      <c r="D67" s="3" t="n">
-        <v>0.925385202821083</v>
+      <c r="B67" s="2" t="n">
+        <v>3.28191663931736</v>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>-9.72352634324465</v>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>-12.5739974184359</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
         <v>70</v>
       </c>
-      <c r="B68" s="3" t="n">
-        <v>3.28191663931736</v>
-      </c>
-      <c r="C68" s="3" t="n">
-        <v>-9.72352634324465</v>
-      </c>
-      <c r="D68" s="3" t="n">
-        <v>-12.5739974184359</v>
+      <c r="B68" s="2" t="n">
+        <v>-3.33651096282173</v>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>6.65665087252976</v>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>10.3320872183514</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
         <v>71</v>
       </c>
-      <c r="B69" s="3" t="n">
-        <v>-3.33651096282173</v>
-      </c>
-      <c r="C69" s="3" t="n">
-        <v>6.65665087252976</v>
-      </c>
-      <c r="D69" s="3" t="n">
-        <v>10.3320872183514</v>
+      <c r="B69" s="2" t="n">
+        <v>1.21630506245891</v>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>6.73962509480983</v>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>5.46868820039552</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="B70" s="3" t="n">
-        <v>1.21630506245891</v>
-      </c>
-      <c r="C70" s="3" t="n">
-        <v>6.73962509480983</v>
-      </c>
-      <c r="D70" s="3" t="n">
-        <v>5.46868820039552</v>
+      <c r="B70" s="2" t="n">
+        <v>-3.70250081195194</v>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>1.38057050045681</v>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>5.25919397984949</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
         <v>73</v>
       </c>
-      <c r="B71" s="3" t="n">
-        <v>-3.70250081195194</v>
-      </c>
-      <c r="C71" s="3" t="n">
-        <v>1.38057050045681</v>
-      </c>
-      <c r="D71" s="3" t="n">
-        <v>5.25919397984949</v>
+      <c r="B71" s="2" t="n">
+        <v>-1.11298482293423</v>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>3.73485531190547</v>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>4.90557298980765</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
         <v>74</v>
       </c>
-      <c r="B72" s="3" t="n">
-        <v>-1.11298482293423</v>
-      </c>
-      <c r="C72" s="3" t="n">
-        <v>3.73485531190547</v>
-      </c>
-      <c r="D72" s="3" t="n">
-        <v>4.90557298980765</v>
+      <c r="B72" s="2" t="n">
+        <v>6.95770804911322</v>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>4.11196911196912</v>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>-2.65124071726136</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
         <v>75</v>
       </c>
-      <c r="B73" s="3" t="n">
-        <v>6.95770804911322</v>
-      </c>
-      <c r="C73" s="3" t="n">
-        <v>4.11196911196912</v>
-      </c>
-      <c r="D73" s="3" t="n">
-        <v>-2.65124071726136</v>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2" t="n">
+        <v>1.60393102169478</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
         <v>76</v>
       </c>
-      <c r="B74" s="3"/>
-      <c r="C74" s="3" t="n">
-        <v>1.60393102169478</v>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2" t="n">
+        <v>-2.90172460990967</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="s">
+      <c r="A75" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B75" s="3"/>
-      <c r="C75" s="3" t="n">
-        <v>-2.90172460990967</v>
-      </c>
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
     </row>
     <row r="76" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="4" t="s">
+      <c r="A76" s="5" t="s">
         <v>78</v>
       </c>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
       <c r="D76" s="5"/>
-    </row>
-    <row r="77" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E76" s="5"/>
+    </row>
+    <row r="77" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="s">
         <v>79</v>
       </c>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
       <c r="D77" s="6"/>
-      <c r="E77" s="6"/>
     </row>
     <row r="78" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="7" t="s">
+      <c r="A78" s="6"/>
+      <c r="B78" s="6"/>
+      <c r="C78" s="6"/>
+      <c r="D78" s="6"/>
+    </row>
+    <row r="79" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B78" s="7"/>
-      <c r="C78" s="7"/>
-      <c r="D78" s="7"/>
-    </row>
-    <row r="79" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="7"/>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
       <c r="D79" s="7"/>
     </row>
     <row r="80" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="8" t="s">
+      <c r="A80" s="7"/>
+      <c r="B80" s="7"/>
+      <c r="C80" s="7"/>
+      <c r="D80" s="7"/>
+    </row>
+    <row r="81" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B80" s="8"/>
-      <c r="C80" s="8"/>
-      <c r="D80" s="8"/>
-    </row>
-    <row r="81" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="8"/>
       <c r="B81" s="8"/>
       <c r="C81" s="8"/>
       <c r="D81" s="8"/>
     </row>
-    <row r="82" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="B82" s="9"/>
-      <c r="C82" s="9"/>
-      <c r="D82" s="9"/>
-    </row>
-    <row r="83" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="9"/>
-      <c r="B83" s="9"/>
-      <c r="C83" s="9"/>
-      <c r="D83" s="9"/>
-    </row>
+    <row r="82" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="8"/>
+      <c r="B82" s="8"/>
+      <c r="C82" s="8"/>
+      <c r="D82" s="8"/>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A77:E77"/>
-    <mergeCell ref="A78:D79"/>
-    <mergeCell ref="A80:D81"/>
-    <mergeCell ref="A82:D83"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A77:D78"/>
+    <mergeCell ref="A79:D80"/>
+    <mergeCell ref="A81:D82"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/agriculture 5.xlsx
+++ b/agriculture 5.xlsx
@@ -20,21 +20,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
-  <si>
-    <t xml:space="preserve">YEAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All-India</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AREA (Million Hectares)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production (Million Tonnes)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yield (Kg./Hectare)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
+  <si>
+    <t xml:space="preserve">Year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yield </t>
   </si>
   <si>
     <t xml:space="preserve">1950-51</t>
@@ -253,13 +250,32 @@
     <t xml:space="preserve">2021-22</t>
   </si>
   <si>
+    <t xml:space="preserve">Unit:- Area - Million Hectares, Product – Metric Ton, Yield – kg./Hector</t>
+  </si>
+  <si>
     <t xml:space="preserve">Source: Economic &amp; Political Weekly Research Foundation -EPWRF (1950-2022)</t>
   </si>
   <si>
-    <t xml:space="preserve">Note:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2016-17 to 2020-21 - Data for the years are Final Estimates as released on 25.05.2022</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Note:- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2016-17 to 2020-21 - Data for the years are Final Estimates as released on 25.05.2022</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">2021-22 to 2021-22 - : All-India:-&gt; Data for the year 2021-22 are 3rd Advance Estimates as released on 19.05.2022 .</t>
@@ -397,16 +413,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -418,11 +446,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -452,1092 +476,1088 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E1048576"/>
-  <sheetFormatPr defaultColWidth="10.78515625" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.8125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.54"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24.8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20.03"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="B3" s="4" t="n">
+        <v>-2.87179487179486</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>-4.33436532507741</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>-1.50476937937695</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>-2.87179487179486</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>-4.33436532507741</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>-1.50476937937695</v>
+      <c r="B4" s="4" t="n">
+        <v>3.80147835269271</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>21.3592233009709</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>16.9141421106667</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>3.80147835269271</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>21.3592233009709</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>16.9141421106667</v>
+      <c r="B5" s="4" t="n">
+        <v>8.646998982706</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>6.93333333333333</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>-1.69993577729137</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>8.646998982706</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>6.93333333333333</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>-1.69993577729137</v>
+      <c r="B6" s="4" t="n">
+        <v>5.43071161048689</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>12.7182044887781</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>7.04533333333335</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>5.43071161048689</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>12.7182044887781</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>7.04533333333335</v>
+      <c r="B7" s="4" t="n">
+        <v>9.85790408525755</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>-3.09734513274336</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>-11.7931343729759</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="2" t="n">
-        <v>9.85790408525755</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>-3.09734513274336</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>-11.7931343729759</v>
+      <c r="B8" s="4" t="n">
+        <v>9.29668552950687</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>7.30593607305936</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>-1.82021012200633</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="2" t="n">
-        <v>9.29668552950687</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>7.30593607305936</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>-1.82021012200633</v>
+      <c r="B9" s="4" t="n">
+        <v>-13.2396449704142</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>-15</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>-1.90861104319185</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="2" t="n">
-        <v>-13.2396449704142</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>-15</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>-1.90861104319185</v>
+      <c r="B10" s="4" t="n">
+        <v>7.58738277919862</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>24.6558197747184</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>15.7214076246334</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="2" t="n">
-        <v>7.58738277919862</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>24.6558197747184</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>15.7214076246334</v>
+      <c r="B11" s="4" t="n">
+        <v>6.02218700475436</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>3.6144578313253</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>-2.18190111755912</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="2" t="n">
-        <v>6.02218700475436</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>3.6144578313253</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>-2.18190111755912</v>
+      <c r="B12" s="4" t="n">
+        <v>-3.36322869955158</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>6.5891472868217</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>10.1981865284974</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>-3.36322869955158</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>6.5891472868217</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>10.1981865284974</v>
+      <c r="B13" s="4" t="n">
+        <v>4.94972931167828</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>9.72727272727274</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>4.61603563997979</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="2" t="n">
-        <v>4.94972931167828</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>9.72727272727274</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>4.61603563997979</v>
+      <c r="B14" s="4" t="n">
+        <v>0.147383935151058</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>-10.6876553438277</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>-10.8730337078652</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="2" t="n">
-        <v>0.147383935151058</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>-10.6876553438277</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>-10.8730337078652</v>
+      <c r="B15" s="4" t="n">
+        <v>-0.662251655629143</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>-8.62708719851577</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>-8.01785106463447</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="2" t="n">
-        <v>-0.662251655629143</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>-8.62708719851577</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>-8.01785106463447</v>
+      <c r="B16" s="4" t="n">
+        <v>-0.592592592592589</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>24.4670050761421</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>25.1319161766923</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="2" t="n">
-        <v>-0.592592592592589</v>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>24.4670050761421</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>25.1319161766923</v>
+      <c r="B17" s="4" t="n">
+        <v>-6.3338301043219</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>-15.1712887438825</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>-9.3789704271632</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="2" t="n">
-        <v>-6.3338301043219</v>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>-15.1712887438825</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>-9.3789704271632</v>
+      <c r="B18" s="4" t="n">
+        <v>2.14797136038185</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>9.51923076923078</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>7.21563508466587</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="2" t="n">
-        <v>2.14797136038185</v>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>9.51923076923078</v>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>7.21563508466587</v>
+      <c r="B19" s="4" t="n">
+        <v>16.7445482866044</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>45.2151009657594</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>24.3870269539044</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="2" t="n">
-        <v>16.7445482866044</v>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>45.2151009657594</v>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>24.3870269539044</v>
+      <c r="B20" s="4" t="n">
+        <v>6.47098065376919</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>12.7569528415961</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>5.90447707087183</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="2" t="n">
-        <v>6.47098065376919</v>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>12.7569528415961</v>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>5.90447707087183</v>
+      <c r="B21" s="4" t="n">
+        <v>4.19799498746867</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>7.7211796246649</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>3.37597877711695</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="2" t="n">
-        <v>4.19799498746867</v>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>7.7211796246649</v>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>3.37597877711695</v>
+      <c r="B22" s="4" t="n">
+        <v>9.68129885748648</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>18.6162269785963</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>8.19536423841059</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="2" t="n">
-        <v>9.68129885748648</v>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>18.6162269785963</v>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>8.19536423841059</v>
+      <c r="B23" s="4" t="n">
+        <v>4.9342105263158</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>10.8266890474192</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>5.57230298393268</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="2" t="n">
-        <v>4.9342105263158</v>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>10.8266890474192</v>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>5.57230298393268</v>
+      <c r="B24" s="4" t="n">
+        <v>1.67189132706373</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>-6.32336236274139</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>-7.86328750643195</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="2" t="n">
-        <v>1.67189132706373</v>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>-6.32336236274139</v>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>-7.86328750643195</v>
+      <c r="B25" s="4" t="n">
+        <v>-4.52209660842756</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>-11.9644300727567</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>-7.79498635287454</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="2" t="n">
-        <v>-4.52209660842756</v>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>-11.9644300727567</v>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>-7.79498635287454</v>
+      <c r="B26" s="4" t="n">
+        <v>-3.06781485468244</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>10.6519742883379</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>14.15421888196</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="2" t="n">
-        <v>-3.06781485468244</v>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>10.6519742883379</v>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>14.15421888196</v>
+      <c r="B27" s="4" t="n">
+        <v>13.5480288728484</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>19.6680497925311</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>5.38953032171281</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="2" t="n">
-        <v>13.5480288728484</v>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>19.6680497925311</v>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>5.38953032171281</v>
+      <c r="B28" s="4" t="n">
+        <v>2.29828850855747</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>0.589459084604727</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>-1.67060208328901</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="2" t="n">
-        <v>2.29828850855747</v>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>0.589459084604727</v>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>-1.67060208328901</v>
+      <c r="B29" s="4" t="n">
+        <v>2.58126195028681</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>9.44501895897967</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>6.72743399845677</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="2" t="n">
-        <v>2.58126195028681</v>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>9.44501895897967</v>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>6.72743399845677</v>
+      <c r="B30" s="4" t="n">
+        <v>5.4986020503262</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>11.8425196850394</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>5.97702702702703</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="2" t="n">
-        <v>5.4986020503262</v>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>11.8425196850394</v>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>5.97702702702703</v>
+      <c r="B31" s="4" t="n">
+        <v>-2.07597173144876</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>-10.3632779498733</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>-8.46307843362279</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="2" t="n">
-        <v>-2.07597173144876</v>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>-10.3632779498733</v>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>-8.46307843362279</v>
+      <c r="B32" s="4" t="n">
+        <v>0.496165990076669</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>14.0747722274584</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>13.5116875156716</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="2" t="n">
-        <v>0.496165990076669</v>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>14.0747722274584</v>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>13.5116875156716</v>
+      <c r="B33" s="4" t="n">
+        <v>-0.628366247755841</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>3.13963095565959</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>3.76079179731363</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="2" t="n">
-        <v>-0.628366247755841</v>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>3.13963095565959</v>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>3.76079179731363</v>
+      <c r="B34" s="4" t="n">
+        <v>6.45889792231256</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>14.2590120160214</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>7.39207569485512</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="2" t="n">
-        <v>6.45889792231256</v>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>14.2590120160214</v>
-      </c>
-      <c r="D35" s="2" t="n">
-        <v>7.39207569485512</v>
+      <c r="B35" s="4" t="n">
+        <v>4.66694951209166</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>6.28651554101425</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>1.48678414096917</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="2" t="n">
-        <v>4.66694951209166</v>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>6.28651554101425</v>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>1.48678414096917</v>
+      <c r="B36" s="4" t="n">
+        <v>-4.49939197405758</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>-3.10026385224273</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>1.46500271296799</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="2" t="n">
-        <v>-4.49939197405758</v>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>-3.10026385224273</v>
-      </c>
-      <c r="D37" s="2" t="n">
-        <v>1.46500271296799</v>
+      <c r="B37" s="4" t="n">
+        <v>-2.37691001697793</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>6.761969593828</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>9.39304812834225</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="2" t="n">
-        <v>-2.37691001697793</v>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>6.761969593828</v>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>9.39304812834225</v>
+      <c r="B38" s="4" t="n">
+        <v>0.565217391304351</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>-5.80233793836343</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>-6.3314838804292</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="2" t="n">
-        <v>0.565217391304351</v>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>-5.80233793836343</v>
-      </c>
-      <c r="D39" s="2" t="n">
-        <v>-6.3314838804292</v>
+      <c r="B39" s="4" t="n">
+        <v>-0.302637267617811</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>4.17418772563176</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>4.49030076247436</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="2" t="n">
-        <v>-0.302637267617811</v>
-      </c>
-      <c r="C40" s="2" t="n">
-        <v>4.17418772563176</v>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>4.49030076247436</v>
+      <c r="B40" s="4" t="n">
+        <v>4.55333911535125</v>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>17.1973142733377</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>12.0933786841277</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="2" t="n">
-        <v>4.55333911535125</v>
-      </c>
-      <c r="C41" s="2" t="n">
-        <v>17.1973142733377</v>
-      </c>
-      <c r="D41" s="2" t="n">
-        <v>12.0933786841277</v>
+      <c r="B41" s="4" t="n">
+        <v>-2.53007051016175</v>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>-7.87285159859545</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>-5.48144187497215</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="A42" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="2" t="n">
-        <v>-2.53007051016175</v>
-      </c>
-      <c r="C42" s="2" t="n">
-        <v>-7.87285159859545</v>
-      </c>
-      <c r="D42" s="2" t="n">
-        <v>-5.48144187497215</v>
+      <c r="B42" s="4" t="n">
+        <v>2.85106382978724</v>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>10.6118355065196</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>7.54544426006938</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="A43" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="2" t="n">
-        <v>2.85106382978724</v>
-      </c>
-      <c r="C43" s="2" t="n">
-        <v>10.6118355065196</v>
-      </c>
-      <c r="D43" s="2" t="n">
-        <v>7.54544426006938</v>
+      <c r="B43" s="4" t="n">
+        <v>-3.76499793131981</v>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>0.997461008342393</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>4.94884585375259</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+      <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B44" s="2" t="n">
-        <v>-3.76499793131981</v>
-      </c>
-      <c r="C44" s="2" t="n">
-        <v>0.997461008342393</v>
-      </c>
-      <c r="D44" s="2" t="n">
-        <v>4.94884585375259</v>
+      <c r="B44" s="4" t="n">
+        <v>5.71797076526224</v>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>2.72939486442809</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>-2.82678428227746</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+      <c r="A45" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="2" t="n">
-        <v>5.71797076526224</v>
-      </c>
-      <c r="C45" s="2" t="n">
-        <v>2.72939486442809</v>
-      </c>
-      <c r="D45" s="2" t="n">
-        <v>-2.82678428227746</v>
+      <c r="B45" s="4" t="n">
+        <v>2.27734851565677</v>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>4.59709840936899</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>2.29695344199161</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+      <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B46" s="2" t="n">
-        <v>2.27734851565677</v>
-      </c>
-      <c r="C46" s="2" t="n">
-        <v>4.59709840936899</v>
-      </c>
-      <c r="D46" s="2" t="n">
-        <v>2.29695344199161</v>
+      <c r="B46" s="4" t="n">
+        <v>2.18687872763419</v>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>9.90975935828875</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>7.52689075630251</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="A47" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B47" s="2" t="n">
-        <v>2.18687872763419</v>
-      </c>
-      <c r="C47" s="2" t="n">
-        <v>9.90975935828875</v>
-      </c>
-      <c r="D47" s="2" t="n">
-        <v>7.52689075630251</v>
+      <c r="B47" s="4" t="n">
+        <v>-2.68482490272373</v>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>-5.5800516953018</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>-2.97482748110692</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+      <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="2" t="n">
-        <v>-2.68482490272373</v>
-      </c>
-      <c r="C48" s="2" t="n">
-        <v>-5.5800516953018</v>
-      </c>
-      <c r="D48" s="2" t="n">
-        <v>-2.97482748110692</v>
+      <c r="B48" s="4" t="n">
+        <v>3.5185925629748</v>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>11.6747181964573</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>7.87874394384234</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+      <c r="A49" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="2" t="n">
-        <v>3.5185925629748</v>
-      </c>
-      <c r="C49" s="2" t="n">
-        <v>11.6747181964573</v>
-      </c>
-      <c r="D49" s="2" t="n">
-        <v>7.87874394384234</v>
+      <c r="B49" s="4" t="n">
+        <v>3.12862108922363</v>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>-4.32588320115357</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>-7.22829495564913</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+      <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B50" s="2" t="n">
-        <v>3.12862108922363</v>
-      </c>
-      <c r="C50" s="2" t="n">
-        <v>-4.32588320115357</v>
-      </c>
-      <c r="D50" s="2" t="n">
-        <v>-7.22829495564913</v>
+      <c r="B50" s="4" t="n">
+        <v>3.07116104868914</v>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>7.44536548605881</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>4.24382902350886</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+      <c r="A51" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="2" t="n">
-        <v>3.07116104868914</v>
-      </c>
-      <c r="C51" s="2" t="n">
-        <v>7.44536548605881</v>
-      </c>
-      <c r="D51" s="2" t="n">
-        <v>4.24382902350886</v>
+      <c r="B51" s="4" t="n">
+        <v>-0.109011627906985</v>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>7.12582409875158</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>7.23881288409869</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
+      <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="2" t="n">
-        <v>-0.109011627906985</v>
-      </c>
-      <c r="C52" s="2" t="n">
-        <v>7.12582409875158</v>
-      </c>
-      <c r="D52" s="2" t="n">
-        <v>7.23881288409869</v>
+      <c r="B52" s="4" t="n">
+        <v>-6.4023281193161</v>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>-8.75998428702369</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>-2.51979841612671</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
+      <c r="A53" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B53" s="2" t="n">
-        <v>-6.4023281193161</v>
-      </c>
-      <c r="C53" s="2" t="n">
-        <v>-8.75998428702369</v>
-      </c>
-      <c r="D53" s="2" t="n">
-        <v>-2.51979841612671</v>
+      <c r="B53" s="4" t="n">
+        <v>2.37077341624563</v>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>4.43455797933408</v>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>1.99409158050221</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
+      <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="2" t="n">
-        <v>2.37077341624563</v>
-      </c>
-      <c r="C54" s="2" t="n">
-        <v>4.43455797933408</v>
-      </c>
-      <c r="D54" s="2" t="n">
-        <v>1.99409158050221</v>
+      <c r="B54" s="4" t="n">
+        <v>-4.32801822323463</v>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>-9.6330905592964</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>-5.52063721940623</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
+      <c r="A55" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B55" s="2" t="n">
-        <v>-4.32801822323463</v>
-      </c>
-      <c r="C55" s="2" t="n">
-        <v>-9.6330905592964</v>
-      </c>
-      <c r="D55" s="2" t="n">
-        <v>-5.52063721940623</v>
+      <c r="B55" s="4" t="n">
+        <v>5.51587301587302</v>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>9.73236009732359</v>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>3.96548024157699</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
+      <c r="A56" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B56" s="2" t="n">
-        <v>5.51587301587302</v>
-      </c>
-      <c r="C56" s="2" t="n">
-        <v>9.73236009732359</v>
-      </c>
-      <c r="D56" s="2" t="n">
-        <v>3.96548024157699</v>
+      <c r="B56" s="4" t="n">
+        <v>-0.789770590447536</v>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>-4.8780487804878</v>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>-4.09141172134169</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
+      <c r="A57" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B57" s="2" t="n">
-        <v>-0.789770590447536</v>
-      </c>
-      <c r="C57" s="2" t="n">
-        <v>-4.8780487804878</v>
-      </c>
-      <c r="D57" s="2" t="n">
-        <v>-4.09141172134169</v>
+      <c r="B57" s="4" t="n">
+        <v>0.379075056861256</v>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>1.03438228438228</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>0.653343581860111</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+      <c r="A58" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B58" s="2" t="n">
-        <v>0.379075056861256</v>
-      </c>
-      <c r="C58" s="2" t="n">
-        <v>1.03438228438228</v>
-      </c>
-      <c r="D58" s="2" t="n">
-        <v>0.653343581860111</v>
+      <c r="B58" s="4" t="n">
+        <v>5.70241691842899</v>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>9.31506849315069</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>3.39480717831233</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+      <c r="A59" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B59" s="2" t="n">
-        <v>5.70241691842899</v>
-      </c>
-      <c r="C59" s="2" t="n">
-        <v>9.31506849315069</v>
-      </c>
-      <c r="D59" s="2" t="n">
-        <v>3.39480717831233</v>
+      <c r="B59" s="4" t="n">
+        <v>0.178635226866741</v>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>3.64068064899088</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>3.47722043937946</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+      <c r="A60" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B60" s="2" t="n">
-        <v>0.178635226866741</v>
-      </c>
-      <c r="C60" s="2" t="n">
-        <v>3.64068064899088</v>
-      </c>
-      <c r="D60" s="2" t="n">
-        <v>3.47722043937946</v>
+      <c r="B60" s="4" t="n">
+        <v>-1.0342368045649</v>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>2.68550337278861</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>3.7486572426813</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+      <c r="A61" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="2" t="n">
-        <v>-1.0342368045649</v>
-      </c>
-      <c r="C61" s="2" t="n">
-        <v>2.68550337278861</v>
-      </c>
-      <c r="D61" s="2" t="n">
-        <v>3.7486572426813</v>
+      <c r="B61" s="4" t="n">
+        <v>2.55855855855855</v>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>0.148735746157658</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>-2.33152512288838</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+      <c r="A62" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B62" s="2" t="n">
-        <v>2.55855855855855</v>
-      </c>
-      <c r="C62" s="2" t="n">
-        <v>0.148735746157658</v>
-      </c>
-      <c r="D62" s="2" t="n">
-        <v>-2.33152512288838</v>
+      <c r="B62" s="4" t="n">
+        <v>2.14335910049193</v>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>7.51237623762377</v>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>5.25194324013059</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+      <c r="A63" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B63" s="2" t="n">
-        <v>2.14335910049193</v>
-      </c>
-      <c r="C63" s="2" t="n">
-        <v>7.51237623762377</v>
-      </c>
-      <c r="D63" s="2" t="n">
-        <v>5.25194324013059</v>
+      <c r="B63" s="4" t="n">
+        <v>2.71757825937393</v>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>9.22067457119833</v>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>6.30895614783584</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
+      <c r="A64" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B64" s="2" t="n">
-        <v>2.71757825937393</v>
-      </c>
-      <c r="C64" s="2" t="n">
-        <v>9.22067457119833</v>
-      </c>
-      <c r="D64" s="2" t="n">
-        <v>6.30895614783584</v>
+      <c r="B64" s="4" t="n">
+        <v>0.468854655056927</v>
+      </c>
+      <c r="C64" s="4" t="n">
+        <v>-1.44392917369307</v>
+      </c>
+      <c r="D64" s="4" t="n">
+        <v>-1.90274442160661</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
+      <c r="A65" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B65" s="2" t="n">
-        <v>0.468854655056927</v>
-      </c>
-      <c r="C65" s="2" t="n">
-        <v>-1.44392917369307</v>
-      </c>
-      <c r="D65" s="2" t="n">
-        <v>-1.90274442160661</v>
+      <c r="B65" s="4" t="n">
+        <v>1.56666666666667</v>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>2.502406159769</v>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>0.925385202821083</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
+      <c r="A66" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B66" s="2" t="n">
-        <v>1.56666666666667</v>
-      </c>
-      <c r="C66" s="2" t="n">
-        <v>2.502406159769</v>
-      </c>
-      <c r="D66" s="2" t="n">
-        <v>0.925385202821083</v>
+      <c r="B66" s="4" t="n">
+        <v>3.28191663931736</v>
+      </c>
+      <c r="C66" s="4" t="n">
+        <v>-9.72352634324465</v>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>-12.5739974184359</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
+      <c r="A67" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B67" s="2" t="n">
-        <v>3.28191663931736</v>
-      </c>
-      <c r="C67" s="2" t="n">
-        <v>-9.72352634324465</v>
-      </c>
-      <c r="D67" s="2" t="n">
-        <v>-12.5739974184359</v>
+      <c r="B67" s="4" t="n">
+        <v>-3.33651096282173</v>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>6.65665087252976</v>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>10.3320872183514</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
+      <c r="A68" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B68" s="2" t="n">
-        <v>-3.33651096282173</v>
-      </c>
-      <c r="C68" s="2" t="n">
-        <v>6.65665087252976</v>
-      </c>
-      <c r="D68" s="2" t="n">
-        <v>10.3320872183514</v>
+      <c r="B68" s="4" t="n">
+        <v>1.21630506245891</v>
+      </c>
+      <c r="C68" s="4" t="n">
+        <v>6.73962509480983</v>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>5.46868820039552</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
+      <c r="A69" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B69" s="2" t="n">
-        <v>1.21630506245891</v>
-      </c>
-      <c r="C69" s="2" t="n">
-        <v>6.73962509480983</v>
-      </c>
-      <c r="D69" s="2" t="n">
-        <v>5.46868820039552</v>
+      <c r="B69" s="4" t="n">
+        <v>-3.70250081195194</v>
+      </c>
+      <c r="C69" s="4" t="n">
+        <v>1.38057050045681</v>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>5.25919397984949</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
+      <c r="A70" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B70" s="2" t="n">
-        <v>-3.70250081195194</v>
-      </c>
-      <c r="C70" s="2" t="n">
-        <v>1.38057050045681</v>
-      </c>
-      <c r="D70" s="2" t="n">
-        <v>5.25919397984949</v>
+      <c r="B70" s="4" t="n">
+        <v>-1.11298482293423</v>
+      </c>
+      <c r="C70" s="4" t="n">
+        <v>3.73485531190547</v>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>4.90557298980765</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="s">
+      <c r="A71" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B71" s="2" t="n">
-        <v>-1.11298482293423</v>
-      </c>
-      <c r="C71" s="2" t="n">
-        <v>3.73485531190547</v>
-      </c>
-      <c r="D71" s="2" t="n">
-        <v>4.90557298980765</v>
+      <c r="B71" s="4" t="n">
+        <v>6.95770804911322</v>
+      </c>
+      <c r="C71" s="4" t="n">
+        <v>4.11196911196912</v>
+      </c>
+      <c r="D71" s="4" t="n">
+        <v>-2.65124071726136</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="s">
+      <c r="A72" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B72" s="2" t="n">
-        <v>6.95770804911322</v>
-      </c>
-      <c r="C72" s="2" t="n">
-        <v>4.11196911196912</v>
-      </c>
-      <c r="D72" s="2" t="n">
-        <v>-2.65124071726136</v>
-      </c>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4" t="n">
+        <v>1.60393102169478</v>
+      </c>
+      <c r="D72" s="3"/>
     </row>
     <row r="73" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="s">
+      <c r="A73" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B73" s="2"/>
-      <c r="C73" s="2" t="n">
-        <v>1.60393102169478</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="s">
+      <c r="B73" s="4"/>
+      <c r="C73" s="4" t="n">
+        <v>-2.90172460990967</v>
+      </c>
+      <c r="D73" s="3"/>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B74" s="2"/>
-      <c r="C74" s="2" t="n">
-        <v>-2.90172460990967</v>
-      </c>
+      <c r="B74" s="5"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
     </row>
     <row r="75" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="3" t="s">
+      <c r="A75" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
-    </row>
-    <row r="76" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="5" t="s">
+      <c r="B75" s="7"/>
+      <c r="C75" s="7"/>
+      <c r="D75" s="7"/>
+    </row>
+    <row r="76" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B76" s="5"/>
-      <c r="C76" s="5"/>
-      <c r="D76" s="5"/>
-      <c r="E76" s="5"/>
+      <c r="B76" s="8"/>
+      <c r="C76" s="8"/>
+      <c r="D76" s="8"/>
     </row>
     <row r="77" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="6" t="s">
+      <c r="A77" s="8"/>
+      <c r="B77" s="8"/>
+      <c r="C77" s="8"/>
+      <c r="D77" s="8"/>
+    </row>
+    <row r="78" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="B77" s="6"/>
-      <c r="C77" s="6"/>
-      <c r="D77" s="6"/>
-    </row>
-    <row r="78" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="6"/>
-      <c r="B78" s="6"/>
-      <c r="C78" s="6"/>
-      <c r="D78" s="6"/>
+      <c r="B78" s="9"/>
+      <c r="C78" s="9"/>
+      <c r="D78" s="9"/>
     </row>
     <row r="79" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="7" t="s">
+      <c r="A79" s="9"/>
+      <c r="B79" s="9"/>
+      <c r="C79" s="9"/>
+      <c r="D79" s="9"/>
+    </row>
+    <row r="80" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="B79" s="7"/>
-      <c r="C79" s="7"/>
-      <c r="D79" s="7"/>
-    </row>
-    <row r="80" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="7"/>
-      <c r="B80" s="7"/>
-      <c r="C80" s="7"/>
-      <c r="D80" s="7"/>
-    </row>
-    <row r="81" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="B81" s="8"/>
-      <c r="C81" s="8"/>
-      <c r="D81" s="8"/>
-    </row>
-    <row r="82" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="8"/>
-      <c r="B82" s="8"/>
-      <c r="C82" s="8"/>
-      <c r="D82" s="8"/>
-    </row>
+      <c r="B80" s="10"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="10"/>
+    </row>
+    <row r="81" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="10"/>
+      <c r="B81" s="10"/>
+      <c r="C81" s="10"/>
+      <c r="D81" s="10"/>
+    </row>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A76:E76"/>
-    <mergeCell ref="A77:D78"/>
-    <mergeCell ref="A79:D80"/>
-    <mergeCell ref="A81:D82"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A76:D77"/>
+    <mergeCell ref="A78:D79"/>
+    <mergeCell ref="A80:D81"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/agriculture 5.xlsx
+++ b/agriculture 5.xlsx
@@ -288,7 +288,6 @@
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Description</t>
     </r>
@@ -298,7 +297,6 @@
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> : Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
     </r>
@@ -312,7 +310,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -343,11 +341,22 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -358,7 +367,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -368,13 +377,6 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin"/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
       <right/>
       <top style="thin"/>
       <bottom/>
@@ -438,20 +440,20 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -476,7 +478,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E1048576"/>
-  <sheetFormatPr defaultColWidth="10.8125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.82421875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.54"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24.8"/>
@@ -1500,51 +1502,51 @@
       <c r="C74" s="5"/>
       <c r="D74" s="5"/>
     </row>
-    <row r="75" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B75" s="7"/>
-      <c r="C75" s="7"/>
-      <c r="D75" s="7"/>
+      <c r="B75" s="6"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="6"/>
     </row>
     <row r="76" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="8" t="s">
+      <c r="A76" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B76" s="8"/>
-      <c r="C76" s="8"/>
-      <c r="D76" s="8"/>
+      <c r="B76" s="7"/>
+      <c r="C76" s="7"/>
+      <c r="D76" s="7"/>
     </row>
     <row r="77" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="8"/>
-      <c r="B77" s="8"/>
-      <c r="C77" s="8"/>
-      <c r="D77" s="8"/>
+      <c r="A77" s="7"/>
+      <c r="B77" s="7"/>
+      <c r="C77" s="7"/>
+      <c r="D77" s="7"/>
     </row>
     <row r="78" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="9" t="s">
+      <c r="A78" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="B78" s="9"/>
-      <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
+      <c r="B78" s="8"/>
+      <c r="C78" s="8"/>
+      <c r="D78" s="8"/>
     </row>
     <row r="79" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="9"/>
-      <c r="B79" s="9"/>
-      <c r="C79" s="9"/>
-      <c r="D79" s="9"/>
+      <c r="A79" s="8"/>
+      <c r="B79" s="8"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="8"/>
     </row>
     <row r="80" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="10" t="s">
+      <c r="A80" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="B80" s="10"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="10"/>
-    </row>
-    <row r="81" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B80" s="9"/>
+      <c r="C80" s="9"/>
+      <c r="D80" s="9"/>
+    </row>
+    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="10"/>
       <c r="B81" s="10"/>
       <c r="C81" s="10"/>
@@ -1553,11 +1555,12 @@
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A75:D75"/>
     <mergeCell ref="A76:D77"/>
     <mergeCell ref="A78:D79"/>
-    <mergeCell ref="A80:D81"/>
+    <mergeCell ref="A80:D80"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
